--- a/2024C/data/result2.xlsx
+++ b/2024C/data/result2.xlsx
@@ -1107,15 +1107,15 @@
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="J8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
@@ -1213,11 +1213,11 @@
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
+      <c r="H10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -1470,17 +1470,19 @@
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
+      <c r="M15" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
-      <c r="P15" s="9" t="n"/>
+      <c r="P15" s="9" t="n">
+        <v>35</v>
+      </c>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
       <c r="S15" s="9" t="n"/>
@@ -1897,13 +1899,13 @@
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
@@ -2101,10 +2103,10 @@
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n">
+      <c r="I27" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
@@ -2166,10 +2168,10 @@
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
-      <c r="W28" s="8" t="n"/>
-      <c r="X28" s="8" t="n">
+      <c r="W28" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
       <c r="Z28" s="8" t="n"/>
       <c r="AA28" s="8" t="n"/>
@@ -2377,10 +2379,10 @@
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
       <c r="U32" s="8" t="n"/>
-      <c r="V32" s="8" t="n"/>
-      <c r="W32" s="8" t="n">
+      <c r="V32" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
       <c r="Z32" s="8" t="n"/>
@@ -2437,7 +2439,7 @@
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
       <c r="Z33" s="9" t="n">
-        <v>1.087</v>
+        <v>1.088</v>
       </c>
       <c r="AA33" s="9" t="n">
         <v>1.091</v>
@@ -2538,16 +2540,16 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n">
+        <v>0.333</v>
+      </c>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
       <c r="AB35" s="9" t="n"/>
@@ -2558,7 +2560,9 @@
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
       <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="9" t="n"/>
+      <c r="AJ35" s="9" t="n">
+        <v>0.29</v>
+      </c>
       <c r="AK35" s="9" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="9" t="n"/>
@@ -2590,9 +2594,7 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
-      <c r="S36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S36" s="8" t="n"/>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
@@ -2604,7 +2606,9 @@
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
-      <c r="AE36" s="8" t="n"/>
+      <c r="AE36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
       <c r="AH36" s="8" t="n"/>
@@ -2646,7 +2650,9 @@
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.03</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
@@ -2654,11 +2660,13 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -2692,14 +2700,14 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
-      <c r="S38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S38" s="8" t="n"/>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
+      <c r="X38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
@@ -2745,12 +2753,12 @@
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
-      <c r="U39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
-      <c r="X39" s="9" t="n"/>
+      <c r="X39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
       <c r="AA39" s="9" t="n"/>
@@ -2796,12 +2804,12 @@
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
-      <c r="U40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
+      <c r="X40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="n"/>
@@ -2847,12 +2855,12 @@
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
-      <c r="U41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
-      <c r="X41" s="9" t="n"/>
+      <c r="X41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="9" t="n"/>
@@ -2896,14 +2904,14 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
-      <c r="S42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S42" s="8" t="n"/>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
+      <c r="X42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -2947,14 +2955,14 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
-      <c r="X43" s="9" t="n"/>
+      <c r="X43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -2998,14 +3006,14 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -3051,12 +3059,12 @@
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
-      <c r="U45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
-      <c r="X45" s="9" t="n"/>
+      <c r="X45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -3102,12 +3110,12 @@
       <c r="R46" s="8" t="n"/>
       <c r="S46" s="8" t="n"/>
       <c r="T46" s="8" t="n"/>
-      <c r="U46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -3457,7 +3465,9 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
+      <c r="S53" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
@@ -3468,9 +3478,7 @@
       <c r="AA53" s="9" t="n"/>
       <c r="AB53" s="9" t="n"/>
       <c r="AC53" s="9" t="n"/>
-      <c r="AD53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD53" s="9" t="n"/>
       <c r="AE53" s="9" t="n"/>
       <c r="AF53" s="9" t="n"/>
       <c r="AG53" s="9" t="n"/>
@@ -3559,7 +3567,9 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
+      <c r="S55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
@@ -3571,9 +3581,7 @@
       <c r="AB55" s="9" t="n"/>
       <c r="AC55" s="9" t="n"/>
       <c r="AD55" s="9" t="n"/>
-      <c r="AE55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE55" s="9" t="n"/>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
       <c r="AH55" s="9" t="n"/>
@@ -3986,7 +3994,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -4878,11 +4888,11 @@
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n"/>
+      <c r="AF81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG81" s="9" t="n"/>
-      <c r="AH81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
       <c r="AJ81" s="9" t="n"/>
       <c r="AK81" s="9" t="n"/>
@@ -4925,12 +4935,12 @@
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n"/>
+      <c r="AC82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
-      <c r="AF82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
       <c r="AI82" s="8" t="n"/>
@@ -4975,10 +4985,10 @@
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
-      <c r="AC83" s="9" t="n">
+      <c r="AC83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD83" s="9" t="n"/>
       <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
@@ -5365,11 +5375,11 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
@@ -5424,13 +5434,13 @@
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n">
-        <v>47.619</v>
+        <v>45.575</v>
       </c>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n">
-        <v>7.381</v>
+        <v>4.721</v>
       </c>
       <c r="P3" s="9" t="n"/>
       <c r="Q3" s="9" t="n"/>
@@ -5469,11 +5479,11 @@
         </is>
       </c>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
@@ -5573,7 +5583,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n">
-        <v>56</v>
+        <v>55.374</v>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -5583,7 +5593,7 @@
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n">
-        <v>12</v>
+        <v>12.626</v>
       </c>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -5675,12 +5685,14 @@
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="D8" s="8" t="n">
+        <v>31.316</v>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n">
-        <v>60</v>
+        <v>28.684</v>
       </c>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="8" t="n"/>
@@ -5726,13 +5738,13 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
+      <c r="H9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
@@ -5777,15 +5789,15 @@
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="J10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -5828,13 +5840,13 @@
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
+      <c r="H11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
@@ -5888,7 +5900,7 @@
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n">
-        <v>25</v>
+        <v>24.578</v>
       </c>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
@@ -5980,11 +5992,15 @@
           <t>B7</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>5.077</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>26.491</v>
+      </c>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>55</v>
+        <v>23.431</v>
       </c>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
@@ -6032,15 +6048,17 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="D15" s="9" t="n">
+        <v>22.045</v>
+      </c>
+      <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="J15" s="9" t="n">
+        <v>21.955</v>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
@@ -6083,10 +6101,12 @@
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="n">
+        <v>24.278</v>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>45.121</v>
+        <v>23.888</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -6097,7 +6117,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>4.879</v>
+        <v>1.835</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -6187,13 +6207,13 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>35</v>
+        <v>25.062</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n">
-        <v>25</v>
+        <v>34.938</v>
       </c>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
@@ -6240,20 +6260,26 @@
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>4.48</v>
+      </c>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n">
-        <v>45</v>
+        <v>26.538</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
-      <c r="O19" s="9" t="n"/>
+      <c r="N19" s="9" t="n">
+        <v>9.486000000000001</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>4.496</v>
+      </c>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
@@ -6346,11 +6372,11 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
+      <c r="H21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -6393,21 +6419,23 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>6.256</v>
-      </c>
-      <c r="D22" s="8" t="n"/>
+        <v>4.206</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>6.894</v>
+      </c>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n">
-        <v>6.944</v>
+        <v>2.831</v>
       </c>
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n">
-        <v>1.8</v>
+        <v>1.069</v>
       </c>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
@@ -6448,9 +6476,11 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D23" s="9" t="n"/>
+        <v>6.233</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>6.767</v>
+      </c>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
@@ -6505,13 +6535,13 @@
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="J24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
@@ -6554,11 +6584,11 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
+      <c r="H25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
@@ -6657,7 +6687,7 @@
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n">
-        <v>20</v>
+        <v>12.703</v>
       </c>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="9" t="n"/>
@@ -6665,7 +6695,9 @@
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
-      <c r="O27" s="9" t="n"/>
+      <c r="O27" s="9" t="n">
+        <v>6.853</v>
+      </c>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
@@ -6719,7 +6751,7 @@
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n">
-        <v>4.587</v>
+        <v>7.556</v>
       </c>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
@@ -6732,7 +6764,7 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n">
-        <v>10.413</v>
+        <v>7.444</v>
       </c>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
@@ -6775,10 +6807,10 @@
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
-      <c r="W29" s="9" t="n"/>
-      <c r="X29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="W29" s="9" t="n">
+        <v>9.975</v>
+      </c>
+      <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
       <c r="AA29" s="9" t="n"/>
@@ -6824,19 +6856,19 @@
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n">
-        <v>13.44</v>
+        <v>10.733</v>
       </c>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n">
-        <v>0.3</v>
+        <v>2.967</v>
       </c>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
       <c r="AB30" s="8" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
@@ -6930,15 +6962,19 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
-      <c r="U32" s="8" t="n"/>
+      <c r="U32" s="8" t="n">
+        <v>3.192</v>
+      </c>
       <c r="V32" s="8" t="n"/>
-      <c r="W32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="n"/>
-      <c r="AA32" s="8" t="n"/>
+      <c r="Z32" s="8" t="n">
+        <v>5.468</v>
+      </c>
+      <c r="AA32" s="8" t="n">
+        <v>1.34</v>
+      </c>
       <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="8" t="n"/>
@@ -6990,20 +7026,20 @@
       <c r="AA33" s="9" t="n"/>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n">
-        <v>0.439</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AD33" s="9" t="n"/>
       <c r="AE33" s="9" t="n"/>
       <c r="AF33" s="9" t="n"/>
       <c r="AG33" s="9" t="n">
-        <v>0.75</v>
+        <v>3.707</v>
       </c>
       <c r="AH33" s="9" t="n"/>
       <c r="AI33" s="9" t="n">
-        <v>0.36</v>
+        <v>2.217</v>
       </c>
       <c r="AJ33" s="9" t="n">
-        <v>0.327</v>
+        <v>0.71</v>
       </c>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="9" t="n"/>
@@ -7037,21 +7073,29 @@
       <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n">
-        <v>22</v>
+        <v>10.587</v>
       </c>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
-      <c r="V34" s="8" t="n"/>
+      <c r="V34" s="8" t="n">
+        <v>10.132</v>
+      </c>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
-      <c r="Y34" s="8" t="n"/>
+      <c r="Y34" s="8" t="n">
+        <v>0.352</v>
+      </c>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
-      <c r="AB34" s="8" t="n"/>
+      <c r="AB34" s="8" t="n">
+        <v>0.296</v>
+      </c>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
-      <c r="AF34" s="8" t="n"/>
+      <c r="AF34" s="8" t="n">
+        <v>0.633</v>
+      </c>
       <c r="AG34" s="8" t="n"/>
       <c r="AH34" s="8" t="n"/>
       <c r="AI34" s="8" t="n"/>
@@ -7189,12 +7233,16 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
+      <c r="S37" s="9" t="n">
+        <v>0.185</v>
+      </c>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.168</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
@@ -7202,11 +7250,13 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.6</v>
+        <v>0.062</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.185</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -7241,13 +7291,15 @@
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n">
-        <v>0.6</v>
+        <v>0.306</v>
       </c>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
+      <c r="X38" s="8" t="n">
+        <v>0.294</v>
+      </c>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
@@ -7394,13 +7446,15 @@
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n">
-        <v>0.6</v>
+        <v>0.313</v>
       </c>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
-      <c r="X41" s="9" t="n"/>
+      <c r="X41" s="9" t="n">
+        <v>0.287</v>
+      </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="9" t="n"/>
@@ -7446,12 +7500,12 @@
       <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="n"/>
       <c r="T42" s="8" t="n"/>
-      <c r="U42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
+      <c r="X42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -7497,12 +7551,12 @@
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
-      <c r="U43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
-      <c r="X43" s="9" t="n"/>
+      <c r="X43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -7548,12 +7602,12 @@
       <c r="R44" s="8" t="n"/>
       <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
-      <c r="U44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.593</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -7597,9 +7651,7 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
@@ -7611,7 +7663,9 @@
       <c r="AB45" s="9" t="n"/>
       <c r="AC45" s="9" t="n"/>
       <c r="AD45" s="9" t="n"/>
-      <c r="AE45" s="9" t="n"/>
+      <c r="AE45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF45" s="9" t="n"/>
       <c r="AG45" s="9" t="n"/>
       <c r="AH45" s="9" t="n"/>
@@ -7648,14 +7702,14 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
-      <c r="S46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S46" s="8" t="n"/>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -7700,7 +7754,7 @@
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="9" t="n">
-        <v>0.6</v>
+        <v>0.233</v>
       </c>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
@@ -7750,14 +7804,14 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
-      <c r="S48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S48" s="8" t="n"/>
       <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
-      <c r="X48" s="8" t="n"/>
+      <c r="X48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y48" s="8" t="n"/>
       <c r="Z48" s="8" t="n"/>
       <c r="AA48" s="8" t="n"/>
@@ -7802,7 +7856,7 @@
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n">
-        <v>0.6</v>
+        <v>0.431</v>
       </c>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
@@ -7815,7 +7869,9 @@
       <c r="AB49" s="9" t="n"/>
       <c r="AC49" s="9" t="n"/>
       <c r="AD49" s="9" t="n"/>
-      <c r="AE49" s="9" t="n"/>
+      <c r="AE49" s="9" t="n">
+        <v>0.169</v>
+      </c>
       <c r="AF49" s="9" t="n"/>
       <c r="AG49" s="9" t="n"/>
       <c r="AH49" s="9" t="n"/>
@@ -7853,7 +7909,7 @@
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
@@ -7904,7 +7960,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.574</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -7954,14 +8010,14 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S52" s="8" t="n"/>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n"/>
+      <c r="X52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
@@ -8005,14 +8061,14 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S53" s="9" t="n"/>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
-      <c r="X53" s="9" t="n"/>
+      <c r="X53" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y53" s="9" t="n"/>
       <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="9" t="n"/>
@@ -8233,10 +8289,10 @@
       <c r="AH57" s="9" t="n"/>
       <c r="AI57" s="9" t="n"/>
       <c r="AJ57" s="9" t="n"/>
-      <c r="AK57" s="9" t="n"/>
-      <c r="AL57" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="AK57" s="9" t="n">
+        <v>9.526999999999999</v>
+      </c>
+      <c r="AL57" s="9" t="n"/>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
       <c r="AO57" s="9" t="n"/>
@@ -8284,7 +8340,7 @@
       <c r="AI58" s="8" t="n"/>
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n">
-        <v>14</v>
+        <v>13.686</v>
       </c>
       <c r="AL58" s="8" t="n"/>
       <c r="AM58" s="8" t="n"/>
@@ -8333,10 +8389,10 @@
       <c r="AH59" s="9" t="n"/>
       <c r="AI59" s="9" t="n"/>
       <c r="AJ59" s="9" t="n"/>
-      <c r="AK59" s="9" t="n"/>
-      <c r="AL59" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="AK59" s="9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n"/>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -8385,7 +8441,7 @@
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n"/>
       <c r="AL60" s="8" t="n">
-        <v>10</v>
+        <v>9.968999999999999</v>
       </c>
       <c r="AM60" s="8" t="n"/>
       <c r="AN60" s="8" t="n"/>
@@ -8436,7 +8492,7 @@
       <c r="AK61" s="9" t="n"/>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="AN61" s="9" t="n"/>
       <c r="AO61" s="9" t="n"/>
@@ -8483,10 +8539,10 @@
       <c r="AH62" s="8" t="n"/>
       <c r="AI62" s="8" t="n"/>
       <c r="AJ62" s="8" t="n"/>
-      <c r="AK62" s="8" t="n"/>
-      <c r="AL62" s="8" t="n">
+      <c r="AK62" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
@@ -8533,10 +8589,10 @@
       <c r="AH63" s="9" t="n"/>
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
-      <c r="AK63" s="9" t="n">
+      <c r="AK63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="AL63" s="9" t="n"/>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -8637,7 +8693,7 @@
       <c r="AL65" s="9" t="n"/>
       <c r="AM65" s="9" t="n"/>
       <c r="AN65" s="9" t="n">
-        <v>0.6</v>
+        <v>0.596</v>
       </c>
       <c r="AO65" s="9" t="n"/>
       <c r="AP65" s="9" t="n"/>
@@ -8687,10 +8743,12 @@
       <c r="AL66" s="8" t="n"/>
       <c r="AM66" s="8" t="n"/>
       <c r="AN66" s="8" t="n">
-        <v>0.6</v>
+        <v>0.512</v>
       </c>
       <c r="AO66" s="8" t="n"/>
-      <c r="AP66" s="8" t="n"/>
+      <c r="AP66" s="8" t="n">
+        <v>0.08799999999999999</v>
+      </c>
       <c r="AQ66" s="8" t="n"/>
     </row>
     <row r="67" ht="12" customHeight="1" s="19">
@@ -8839,9 +8897,11 @@
       <c r="AN69" s="9" t="n"/>
       <c r="AO69" s="9" t="n"/>
       <c r="AP69" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ69" s="9" t="n"/>
+        <v>0.576</v>
+      </c>
+      <c r="AQ69" s="9" t="n">
+        <v>0.024</v>
+      </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="19">
       <c r="B70" s="10" t="inlineStr">
@@ -8987,10 +9047,12 @@
       <c r="AL72" s="8" t="n"/>
       <c r="AM72" s="8" t="n"/>
       <c r="AN72" s="8" t="n"/>
-      <c r="AO72" s="8" t="n"/>
+      <c r="AO72" s="8" t="n">
+        <v>0.012</v>
+      </c>
       <c r="AP72" s="8" t="n"/>
       <c r="AQ72" s="8" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="19">
@@ -9136,11 +9198,13 @@
       <c r="AK75" s="9" t="n"/>
       <c r="AL75" s="9" t="n"/>
       <c r="AM75" s="9" t="n"/>
-      <c r="AN75" s="9" t="n"/>
+      <c r="AN75" s="9" t="n">
+        <v>0.146</v>
+      </c>
       <c r="AO75" s="9" t="n"/>
       <c r="AP75" s="9" t="n"/>
       <c r="AQ75" s="9" t="n">
-        <v>0.6</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1" s="19">
@@ -9236,9 +9300,11 @@
       <c r="AK77" s="9" t="n"/>
       <c r="AL77" s="9" t="n"/>
       <c r="AM77" s="9" t="n"/>
-      <c r="AN77" s="9" t="n"/>
+      <c r="AN77" s="9" t="n">
+        <v>0.003</v>
+      </c>
       <c r="AO77" s="9" t="n">
-        <v>0.6</v>
+        <v>0.597</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -9288,7 +9354,7 @@
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n"/>
       <c r="AO78" s="8" t="n">
-        <v>0.6</v>
+        <v>0.592</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -9338,7 +9404,7 @@
       <c r="AM79" s="9" t="n"/>
       <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.514</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -9374,11 +9440,11 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
-      <c r="AB80" s="8" t="n">
+      <c r="AB80" s="8" t="n"/>
+      <c r="AC80" s="8" t="n"/>
+      <c r="AD80" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AC80" s="8" t="n"/>
-      <c r="AD80" s="8" t="n"/>
       <c r="AE80" s="8" t="n"/>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
@@ -9426,13 +9492,13 @@
       <c r="AA81" s="9" t="n"/>
       <c r="AB81" s="9" t="n"/>
       <c r="AC81" s="9" t="n"/>
-      <c r="AD81" s="9" t="n"/>
+      <c r="AD81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AE81" s="9" t="n"/>
       <c r="AF81" s="9" t="n"/>
       <c r="AG81" s="9" t="n"/>
-      <c r="AH81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
       <c r="AJ81" s="9" t="n"/>
       <c r="AK81" s="9" t="n"/>
@@ -9476,11 +9542,11 @@
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
       <c r="AC82" s="8" t="n"/>
-      <c r="AD82" s="8" t="n"/>
+      <c r="AD82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AE82" s="8" t="n"/>
-      <c r="AF82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
       <c r="AI82" s="8" t="n"/>
@@ -9525,10 +9591,10 @@
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
-      <c r="AC83" s="9" t="n">
+      <c r="AC83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD83" s="9" t="n"/>
       <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
@@ -9919,10 +9985,10 @@
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n">
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
       <c r="L2" s="8" t="n"/>
@@ -9968,7 +10034,7 @@
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="9" t="n">
-        <v>55</v>
+        <v>52.638</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
@@ -10025,7 +10091,7 @@
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n">
-        <v>35</v>
+        <v>34.94</v>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
@@ -10068,13 +10134,15 @@
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n">
-        <v>72</v>
-      </c>
+      <c r="D5" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
+      <c r="H5" s="9" t="n">
+        <v>36</v>
+      </c>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
@@ -10123,10 +10191,10 @@
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n">
+      <c r="H6" s="8" t="n">
         <v>68</v>
       </c>
+      <c r="I6" s="8" t="n"/>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
@@ -10171,7 +10239,7 @@
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n">
-        <v>43.7</v>
+        <v>36.404</v>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -10184,7 +10252,7 @@
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n">
-        <v>11.3</v>
+        <v>18.596</v>
       </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
@@ -10223,14 +10291,14 @@
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
+      <c r="I8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
@@ -10274,13 +10342,15 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="D9" s="9" t="n">
+        <v>23.117</v>
+      </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n">
-        <v>46</v>
+        <v>22.883</v>
       </c>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
@@ -10325,14 +10395,16 @@
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="H10" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
@@ -10376,7 +10448,9 @@
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="D11" s="9" t="n">
+        <v>13.572</v>
+      </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
@@ -10385,12 +10459,12 @@
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n">
-        <v>25</v>
+        <v>12.872</v>
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n">
-        <v>3</v>
+        <v>1.556</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -10429,11 +10503,13 @@
         </is>
       </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="n">
+        <v>12.543</v>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>25</v>
+        <v>12.457</v>
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -10483,7 +10559,7 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n">
-        <v>86</v>
+        <v>84.96899999999999</v>
       </c>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
@@ -10587,14 +10663,14 @@
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n">
-        <v>37.421</v>
+        <v>38.695</v>
       </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n">
-        <v>6.579</v>
+        <v>5.305</v>
       </c>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
@@ -10693,15 +10769,13 @@
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n">
-        <v>22.895</v>
+        <v>25</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n">
-        <v>2.105</v>
-      </c>
+      <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
@@ -10743,21 +10817,17 @@
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
+      <c r="H18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n">
-        <v>13.25</v>
-      </c>
+      <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n">
-        <v>11.75</v>
-      </c>
+      <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
-      <c r="P18" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="P18" s="8" t="n"/>
       <c r="Q18" s="8" t="n"/>
       <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="n"/>
@@ -10793,14 +10863,14 @@
           <t>B12</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
+      <c r="H19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
@@ -10845,12 +10915,12 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>13.172</v>
+        <v>10.239</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>14.121</v>
+        <v>13.863</v>
       </c>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
@@ -10859,9 +10929,11 @@
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n">
-        <v>7.707</v>
-      </c>
-      <c r="N20" s="8" t="n"/>
+        <v>8.239000000000001</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>0.666</v>
+      </c>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="n"/>
@@ -10904,11 +10976,11 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -10957,11 +11029,11 @@
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n">
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
@@ -11007,11 +11079,11 @@
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
@@ -11057,15 +11129,17 @@
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
+      <c r="K24" s="8" t="n">
+        <v>0.451</v>
+      </c>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
+      <c r="N24" s="8" t="n">
+        <v>4.927</v>
+      </c>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
@@ -11104,7 +11178,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>18</v>
+        <v>17.457</v>
       </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
@@ -11155,7 +11229,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>27</v>
+        <v>26.23</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
@@ -11206,7 +11280,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>20</v>
+        <v>17.804</v>
       </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
@@ -11277,7 +11351,7 @@
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n">
-        <v>15</v>
+        <v>14.768</v>
       </c>
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
@@ -11328,15 +11402,15 @@
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
       <c r="W29" s="9" t="n"/>
-      <c r="X29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
       <c r="AA29" s="9" t="n"/>
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
-      <c r="AD29" s="9" t="n"/>
+      <c r="AD29" s="9" t="n">
+        <v>9.958</v>
+      </c>
       <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
       <c r="AG29" s="9" t="n"/>
@@ -11375,12 +11449,12 @@
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n">
-        <v>5.68</v>
+        <v>7.943</v>
       </c>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n">
-        <v>8.32</v>
+        <v>6.057</v>
       </c>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
@@ -11480,11 +11554,11 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n">
-        <v>7.44</v>
+        <v>7.238</v>
       </c>
       <c r="U32" s="8" t="n"/>
       <c r="V32" s="8" t="n">
-        <v>2.56</v>
+        <v>1.96</v>
       </c>
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
@@ -11494,7 +11568,9 @@
       <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="8" t="n"/>
-      <c r="AE32" s="8" t="n"/>
+      <c r="AE32" s="8" t="n">
+        <v>0.801</v>
+      </c>
       <c r="AF32" s="8" t="n"/>
       <c r="AG32" s="8" t="n"/>
       <c r="AH32" s="8" t="n"/>
@@ -11534,19 +11610,19 @@
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n">
-        <v>2.16</v>
+        <v>2.673</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>4.12</v>
+        <v>5.874</v>
       </c>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
       <c r="Z33" s="9" t="n">
-        <v>1.087</v>
+        <v>1.093</v>
       </c>
       <c r="AA33" s="9" t="n">
-        <v>1.091</v>
+        <v>2.36</v>
       </c>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n"/>
@@ -11593,20 +11669,26 @@
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
+      <c r="X34" s="8" t="n">
+        <v>4.084</v>
+      </c>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
-      <c r="AC34" s="8" t="n"/>
-      <c r="AD34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="AC34" s="8" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
-      <c r="AG34" s="8" t="n"/>
+      <c r="AG34" s="8" t="n">
+        <v>1.363</v>
+      </c>
       <c r="AH34" s="8" t="n"/>
-      <c r="AI34" s="8" t="n"/>
+      <c r="AI34" s="8" t="n">
+        <v>0.455</v>
+      </c>
       <c r="AJ34" s="8" t="n"/>
       <c r="AK34" s="8" t="n"/>
       <c r="AL34" s="8" t="n"/>
@@ -11638,27 +11720,33 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n">
+        <v>0.889</v>
+      </c>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n">
+        <v>1.293</v>
+      </c>
       <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="AD35" s="9" t="n">
+        <v>1.146</v>
+      </c>
       <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
       <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="9" t="n"/>
+      <c r="AJ35" s="9" t="n">
+        <v>0.161</v>
+      </c>
       <c r="AK35" s="9" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="9" t="n"/>
@@ -11743,22 +11831,26 @@
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
-      <c r="U37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.037</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="9" t="n"/>
+      <c r="AE37" s="9" t="n">
+        <v>0.263</v>
+      </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -11797,16 +11889,16 @@
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
+      <c r="X38" s="8" t="n">
+        <v>0.596</v>
+      </c>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
       <c r="AB38" s="8" t="n"/>
       <c r="AC38" s="8" t="n"/>
       <c r="AD38" s="8" t="n"/>
-      <c r="AE38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE38" s="8" t="n"/>
       <c r="AF38" s="8" t="n"/>
       <c r="AG38" s="8" t="n"/>
       <c r="AH38" s="8" t="n"/>
@@ -11848,16 +11940,18 @@
       <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
-      <c r="X39" s="9" t="n"/>
+      <c r="X39" s="9" t="n">
+        <v>0.39</v>
+      </c>
       <c r="Y39" s="9" t="n"/>
-      <c r="Z39" s="9" t="n"/>
+      <c r="Z39" s="9" t="n">
+        <v>0.21</v>
+      </c>
       <c r="AA39" s="9" t="n"/>
       <c r="AB39" s="9" t="n"/>
       <c r="AC39" s="9" t="n"/>
       <c r="AD39" s="9" t="n"/>
-      <c r="AE39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE39" s="9" t="n"/>
       <c r="AF39" s="9" t="n"/>
       <c r="AG39" s="9" t="n"/>
       <c r="AH39" s="9" t="n"/>
@@ -11896,12 +11990,12 @@
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
-      <c r="U40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
+      <c r="X40" s="8" t="n">
+        <v>0.582</v>
+      </c>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="n"/>
@@ -11947,12 +12041,12 @@
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
-      <c r="U41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
-      <c r="X41" s="9" t="n"/>
+      <c r="X41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="9" t="n"/>
@@ -11997,13 +12091,15 @@
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="n">
-        <v>0.6</v>
+        <v>0.374</v>
       </c>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
+      <c r="X42" s="8" t="n">
+        <v>0.226</v>
+      </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -12048,13 +12144,15 @@
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="9" t="n">
-        <v>0.6</v>
+        <v>0.305</v>
       </c>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
-      <c r="X43" s="9" t="n"/>
+      <c r="X43" s="9" t="n">
+        <v>0.295</v>
+      </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -12099,13 +12197,15 @@
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
       <c r="S44" s="8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -12149,11 +12249,11 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n"/>
+      <c r="S45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T45" s="9" t="n"/>
-      <c r="U45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
       <c r="X45" s="9" t="n"/>
@@ -12200,11 +12300,11 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
-      <c r="S46" s="8" t="n"/>
+      <c r="S46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T46" s="8" t="n"/>
-      <c r="U46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
       <c r="X46" s="8" t="n"/>
@@ -12251,14 +12351,14 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
-      <c r="S47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
-      <c r="X47" s="9" t="n"/>
+      <c r="X47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y47" s="9" t="n"/>
       <c r="Z47" s="9" t="n"/>
       <c r="AA47" s="9" t="n"/>
@@ -12303,9 +12403,11 @@
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T48" s="8" t="n"/>
+        <v>0.316</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>0.284</v>
+      </c>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
@@ -12405,7 +12507,7 @@
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n">
-        <v>0.6</v>
+        <v>0.582</v>
       </c>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
@@ -12456,7 +12558,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -12506,14 +12608,14 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S52" s="8" t="n"/>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n"/>
+      <c r="X52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
@@ -12557,14 +12659,14 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
+      <c r="S53" s="9" t="n">
+        <v>0.576</v>
+      </c>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
-      <c r="X53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X53" s="9" t="n"/>
       <c r="Y53" s="9" t="n"/>
       <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="9" t="n"/>
@@ -12609,7 +12711,7 @@
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
       <c r="S54" s="8" t="n">
-        <v>0.6</v>
+        <v>0.548</v>
       </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
@@ -12660,7 +12762,7 @@
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="9" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
@@ -12786,10 +12888,10 @@
       <c r="AI57" s="9" t="n"/>
       <c r="AJ57" s="9" t="n"/>
       <c r="AK57" s="9" t="n"/>
-      <c r="AL57" s="9" t="n"/>
-      <c r="AM57" s="9" t="n">
+      <c r="AL57" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
       <c r="AO57" s="9" t="n"/>
       <c r="AP57" s="9" t="n"/>
@@ -12837,7 +12939,7 @@
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n"/>
       <c r="AL58" s="8" t="n">
-        <v>14</v>
+        <v>13.613</v>
       </c>
       <c r="AM58" s="8" t="n"/>
       <c r="AN58" s="8" t="n"/>
@@ -12888,7 +12990,7 @@
       <c r="AK59" s="9" t="n"/>
       <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n">
-        <v>6</v>
+        <v>5.695</v>
       </c>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -12986,7 +13088,7 @@
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="9" t="n"/>
       <c r="AK61" s="9" t="n">
-        <v>5</v>
+        <v>5.527</v>
       </c>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n"/>
@@ -13036,10 +13138,10 @@
       <c r="AI62" s="8" t="n"/>
       <c r="AJ62" s="8" t="n"/>
       <c r="AK62" s="8" t="n"/>
-      <c r="AL62" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM62" s="8" t="n"/>
+      <c r="AL62" s="8" t="n"/>
+      <c r="AM62" s="8" t="n">
+        <v>6.324</v>
+      </c>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
       <c r="AP62" s="8" t="n"/>
@@ -13086,7 +13188,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>1.447</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -13187,7 +13291,7 @@
       <c r="AL65" s="9" t="n"/>
       <c r="AM65" s="9" t="n"/>
       <c r="AN65" s="9" t="n">
-        <v>0.6</v>
+        <v>0.577</v>
       </c>
       <c r="AO65" s="9" t="n"/>
       <c r="AP65" s="9" t="n"/>
@@ -13237,11 +13341,13 @@
       <c r="AL66" s="8" t="n"/>
       <c r="AM66" s="8" t="n"/>
       <c r="AN66" s="8" t="n">
-        <v>0.6</v>
+        <v>0.572</v>
       </c>
       <c r="AO66" s="8" t="n"/>
       <c r="AP66" s="8" t="n"/>
-      <c r="AQ66" s="8" t="n"/>
+      <c r="AQ66" s="8" t="n">
+        <v>0.026</v>
+      </c>
     </row>
     <row r="67" ht="12" customHeight="1" s="19">
       <c r="B67" s="10" t="inlineStr">
@@ -13289,7 +13395,7 @@
       <c r="AN67" s="9" t="n"/>
       <c r="AO67" s="9" t="n"/>
       <c r="AP67" s="9" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="AQ67" s="9" t="n"/>
     </row>
@@ -13389,9 +13495,11 @@
       <c r="AN69" s="9" t="n"/>
       <c r="AO69" s="9" t="n"/>
       <c r="AP69" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ69" s="9" t="n"/>
+        <v>0.573</v>
+      </c>
+      <c r="AQ69" s="9" t="n">
+        <v>0.027</v>
+      </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="19">
       <c r="B70" s="10" t="inlineStr">
@@ -13436,11 +13544,13 @@
       <c r="AK70" s="8" t="n"/>
       <c r="AL70" s="8" t="n"/>
       <c r="AM70" s="8" t="n"/>
-      <c r="AN70" s="8" t="n"/>
+      <c r="AN70" s="8" t="n">
+        <v>0.027</v>
+      </c>
       <c r="AO70" s="8" t="n"/>
       <c r="AP70" s="8" t="n"/>
       <c r="AQ70" s="8" t="n">
-        <v>0.6</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="19">
@@ -13487,10 +13597,14 @@
       <c r="AL71" s="9" t="n"/>
       <c r="AM71" s="9" t="n"/>
       <c r="AN71" s="9" t="n"/>
-      <c r="AO71" s="9" t="n"/>
-      <c r="AP71" s="9" t="n"/>
+      <c r="AO71" s="9" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AP71" s="9" t="n">
+        <v>0.005</v>
+      </c>
       <c r="AQ71" s="9" t="n">
-        <v>0.6</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="19">
@@ -13538,9 +13652,11 @@
       <c r="AM72" s="8" t="n"/>
       <c r="AN72" s="8" t="n"/>
       <c r="AO72" s="8" t="n"/>
-      <c r="AP72" s="8" t="n"/>
+      <c r="AP72" s="8" t="n">
+        <v>0.056</v>
+      </c>
       <c r="AQ72" s="8" t="n">
-        <v>0.6</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="19">
@@ -13740,7 +13856,7 @@
       <c r="AO76" s="8" t="n"/>
       <c r="AP76" s="8" t="n"/>
       <c r="AQ76" s="8" t="n">
-        <v>0.6</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="77" ht="12" customHeight="1" s="19">
@@ -13788,7 +13904,7 @@
       <c r="AM77" s="9" t="n"/>
       <c r="AN77" s="9" t="n"/>
       <c r="AO77" s="9" t="n">
-        <v>0.6</v>
+        <v>0.593</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -13836,9 +13952,11 @@
       <c r="AK78" s="8" t="n"/>
       <c r="AL78" s="8" t="n"/>
       <c r="AM78" s="8" t="n"/>
-      <c r="AN78" s="8" t="n"/>
+      <c r="AN78" s="8" t="n">
+        <v>0.078</v>
+      </c>
       <c r="AO78" s="8" t="n">
-        <v>0.6</v>
+        <v>0.522</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -13888,7 +14006,7 @@
       <c r="AM79" s="9" t="n"/>
       <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -13924,12 +14042,12 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
-      <c r="AB80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB80" s="8" t="n"/>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
-      <c r="AE80" s="8" t="n"/>
+      <c r="AE80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
       <c r="AH80" s="8" t="n"/>
@@ -13978,11 +14096,11 @@
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n"/>
+      <c r="AF81" s="9" t="n">
+        <v>0.579</v>
+      </c>
       <c r="AG81" s="9" t="n"/>
-      <c r="AH81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
       <c r="AJ81" s="9" t="n"/>
       <c r="AK81" s="9" t="n"/>
@@ -14025,12 +14143,12 @@
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n"/>
+      <c r="AC82" s="8" t="n">
+        <v>0.592</v>
+      </c>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
-      <c r="AF82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
       <c r="AI82" s="8" t="n"/>
@@ -14075,10 +14193,10 @@
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
-      <c r="AC83" s="9" t="n">
+      <c r="AC83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD83" s="9" t="n"/>
       <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
@@ -14465,13 +14583,13 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
@@ -14524,13 +14642,13 @@
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n">
-        <v>47.619</v>
+        <v>49.282</v>
       </c>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n">
-        <v>7.381</v>
+        <v>5.718</v>
       </c>
       <c r="P3" s="9" t="n"/>
       <c r="Q3" s="9" t="n"/>
@@ -14570,7 +14688,7 @@
       </c>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n">
-        <v>35</v>
+        <v>34.748</v>
       </c>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
@@ -14673,7 +14791,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n">
-        <v>56</v>
+        <v>55.763</v>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -14683,7 +14801,7 @@
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n">
-        <v>12</v>
+        <v>11.988</v>
       </c>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -14779,11 +14897,11 @@
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
+      <c r="H8" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
@@ -14826,13 +14944,13 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
+      <c r="H9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
@@ -14877,15 +14995,17 @@
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="I10" s="8" t="n">
+        <v>4.218</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>35.782</v>
+      </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -14928,18 +15048,20 @@
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
+      <c r="H11" s="9" t="n">
+        <v>27.162</v>
+      </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
+      <c r="M11" s="9" t="n">
+        <v>0.838</v>
+      </c>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
@@ -15084,9 +15206,11 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="G14" s="8" t="n"/>
+        <v>52.387</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>2.613</v>
+      </c>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
@@ -15132,15 +15256,15 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="J15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
@@ -15186,7 +15310,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>45.121</v>
+        <v>44.805</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -15197,7 +15321,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>4.879</v>
+        <v>5.195</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -15236,11 +15360,13 @@
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>11.965</v>
+      </c>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
-        <v>25</v>
+        <v>11.949</v>
       </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -15248,7 +15374,9 @@
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
+      <c r="N17" s="9" t="n">
+        <v>1.084</v>
+      </c>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
@@ -15287,7 +15415,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>60</v>
+        <v>58.015</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
@@ -15342,17 +15470,19 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
+      <c r="N19" s="9" t="n">
+        <v>11.585</v>
+      </c>
       <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
+      <c r="P19" s="9" t="n">
+        <v>33.415</v>
+      </c>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="9" t="n"/>
@@ -15393,10 +15523,10 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n">
+      <c r="H20" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
@@ -15440,7 +15570,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>20</v>
+        <v>18.655</v>
       </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
@@ -15501,12 +15631,12 @@
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n">
+        <v>14.811</v>
+      </c>
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
       <c r="T22" s="8" t="n"/>
@@ -15547,20 +15677,18 @@
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n">
-        <v>6.944</v>
+        <v>8.634</v>
       </c>
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n">
-        <v>6.053</v>
+        <v>4.111</v>
       </c>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="9" t="n"/>
@@ -15597,7 +15725,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>15</v>
+        <v>14.987</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
@@ -15653,10 +15781,10 @@
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n">
+      <c r="I25" s="9" t="n">
         <v>18</v>
       </c>
+      <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
@@ -15754,11 +15882,11 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n">
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
@@ -15816,10 +15944,10 @@
       <c r="P28" s="8" t="n"/>
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
-      <c r="S28" s="8" t="n"/>
-      <c r="T28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="S28" s="8" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
@@ -15829,7 +15957,9 @@
       <c r="AA28" s="8" t="n"/>
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
-      <c r="AD28" s="8" t="n"/>
+      <c r="AD28" s="8" t="n">
+        <v>10.55</v>
+      </c>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
       <c r="AG28" s="8" t="n"/>
@@ -15867,13 +15997,15 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n"/>
-      <c r="T29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="S29" s="9" t="n">
+        <v>5.045</v>
+      </c>
+      <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
-      <c r="W29" s="9" t="n"/>
+      <c r="W29" s="9" t="n">
+        <v>4.955</v>
+      </c>
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
@@ -15919,17 +16051,21 @@
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
-      <c r="T30" s="8" t="n"/>
+      <c r="T30" s="8" t="n">
+        <v>12.613</v>
+      </c>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n">
-        <v>14</v>
+        <v>0.597</v>
       </c>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n">
+        <v>0.79</v>
+      </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
@@ -15973,16 +16109,16 @@
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
-      <c r="W31" s="9" t="n"/>
+      <c r="W31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="X31" s="9" t="n"/>
       <c r="Y31" s="9" t="n"/>
       <c r="Z31" s="9" t="n"/>
       <c r="AA31" s="9" t="n"/>
       <c r="AB31" s="9" t="n"/>
       <c r="AC31" s="9" t="n"/>
-      <c r="AD31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="AD31" s="9" t="n"/>
       <c r="AE31" s="9" t="n"/>
       <c r="AF31" s="9" t="n"/>
       <c r="AG31" s="9" t="n"/>
@@ -16022,17 +16158,25 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
-      <c r="U32" s="8" t="n"/>
+      <c r="U32" s="8" t="n">
+        <v>2.282</v>
+      </c>
       <c r="V32" s="8" t="n"/>
       <c r="W32" s="8" t="n">
-        <v>10</v>
+        <v>0.171</v>
       </c>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="n"/>
-      <c r="AA32" s="8" t="n"/>
+      <c r="Z32" s="8" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="AA32" s="8" t="n">
+        <v>1.611</v>
+      </c>
       <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="8" t="n"/>
+      <c r="AC32" s="8" t="n">
+        <v>0.153</v>
+      </c>
       <c r="AD32" s="8" t="n"/>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
@@ -16078,7 +16222,7 @@
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n">
-        <v>0.333</v>
+        <v>1.183</v>
       </c>
       <c r="Z33" s="9" t="n"/>
       <c r="AA33" s="9" t="n"/>
@@ -16088,14 +16232,14 @@
       <c r="AE33" s="9" t="n"/>
       <c r="AF33" s="9" t="n"/>
       <c r="AG33" s="9" t="n">
-        <v>0.75</v>
+        <v>1.523</v>
       </c>
       <c r="AH33" s="9" t="n"/>
       <c r="AI33" s="9" t="n">
-        <v>0.36</v>
+        <v>0.891</v>
       </c>
       <c r="AJ33" s="9" t="n">
-        <v>0.327</v>
+        <v>1.541</v>
       </c>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="9" t="n"/>
@@ -16127,29 +16271,23 @@
       <c r="O34" s="8" t="n"/>
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="n"/>
-      <c r="R34" s="8" t="n"/>
-      <c r="S34" s="8" t="n">
-        <v>0.18</v>
-      </c>
+      <c r="R34" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
-      <c r="V34" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
-      <c r="AB34" s="8" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
-      <c r="AF34" s="8" t="n">
-        <v>0.037</v>
-      </c>
+      <c r="AF34" s="8" t="n"/>
       <c r="AG34" s="8" t="n"/>
       <c r="AH34" s="8" t="n"/>
       <c r="AI34" s="8" t="n"/>
@@ -16184,10 +16322,10 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n">
+      <c r="R35" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
@@ -16249,7 +16387,7 @@
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
       <c r="AE36" s="8" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
@@ -16294,19 +16432,25 @@
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="9" t="n"/>
       <c r="Y37" s="9" t="n"/>
-      <c r="Z37" s="9" t="n"/>
+      <c r="Z37" s="9" t="n">
+        <v>0.064</v>
+      </c>
       <c r="AA37" s="9" t="n"/>
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.6</v>
+        <v>0.295</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.128</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
-      <c r="AJ37" s="9" t="n"/>
+      <c r="AJ37" s="9" t="n">
+        <v>0.015</v>
+      </c>
       <c r="AK37" s="9" t="n"/>
       <c r="AL37" s="9" t="n"/>
       <c r="AM37" s="9" t="n"/>
@@ -16338,14 +16482,14 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
-      <c r="S38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S38" s="8" t="n"/>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
+      <c r="X38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
@@ -16389,14 +16533,16 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T39" s="9" t="n"/>
+      <c r="S39" s="9" t="n"/>
+      <c r="T39" s="9" t="n">
+        <v>0.109</v>
+      </c>
       <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
-      <c r="X39" s="9" t="n"/>
+      <c r="X39" s="9" t="n">
+        <v>0.491</v>
+      </c>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
       <c r="AA39" s="9" t="n"/>
@@ -16440,14 +16586,14 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
-      <c r="S40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
+      <c r="X40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="n"/>
@@ -16491,14 +16637,14 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
-      <c r="X41" s="9" t="n"/>
+      <c r="X41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="9" t="n"/>
@@ -16544,12 +16690,12 @@
       <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="n"/>
       <c r="T42" s="8" t="n"/>
-      <c r="U42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
+      <c r="X42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -16595,12 +16741,12 @@
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
-      <c r="U43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
-      <c r="X43" s="9" t="n"/>
+      <c r="X43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -16646,12 +16792,12 @@
       <c r="R44" s="8" t="n"/>
       <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
-      <c r="U44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -16695,14 +16841,14 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
-      <c r="X45" s="9" t="n"/>
+      <c r="X45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -16746,14 +16892,14 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
-      <c r="S46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S46" s="8" t="n"/>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="8" t="n">
+        <v>0.579</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -16900,7 +17046,7 @@
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
@@ -17002,7 +17148,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -17053,7 +17199,7 @@
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
       <c r="S52" s="8" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
@@ -17103,14 +17249,14 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
+      <c r="S53" s="9" t="n">
+        <v>0.597</v>
+      </c>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
-      <c r="X53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X53" s="9" t="n"/>
       <c r="Y53" s="9" t="n"/>
       <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="9" t="n"/>
@@ -17154,16 +17300,18 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
+      <c r="S54" s="8" t="n">
+        <v>0.496</v>
+      </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
       <c r="W54" s="8" t="n"/>
-      <c r="X54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X54" s="8" t="n"/>
       <c r="Y54" s="8" t="n"/>
-      <c r="Z54" s="8" t="n"/>
+      <c r="Z54" s="8" t="n">
+        <v>0.104</v>
+      </c>
       <c r="AA54" s="8" t="n"/>
       <c r="AB54" s="8" t="n"/>
       <c r="AC54" s="8" t="n"/>
@@ -17205,14 +17353,14 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
+      <c r="S55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
       <c r="W55" s="9" t="n"/>
-      <c r="X55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X55" s="9" t="n"/>
       <c r="Y55" s="9" t="n"/>
       <c r="Z55" s="9" t="n"/>
       <c r="AA55" s="9" t="n"/>
@@ -17283,7 +17431,7 @@
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n"/>
       <c r="AL56" s="8" t="n">
-        <v>15</v>
+        <v>14.694</v>
       </c>
       <c r="AM56" s="8" t="n"/>
       <c r="AN56" s="8" t="n"/>
@@ -17331,10 +17479,10 @@
       <c r="AH57" s="9" t="n"/>
       <c r="AI57" s="9" t="n"/>
       <c r="AJ57" s="9" t="n"/>
-      <c r="AK57" s="9" t="n"/>
-      <c r="AL57" s="9" t="n">
+      <c r="AK57" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="AL57" s="9" t="n"/>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
       <c r="AO57" s="9" t="n"/>
@@ -17382,7 +17530,7 @@
       <c r="AI58" s="8" t="n"/>
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n">
-        <v>14</v>
+        <v>13.84</v>
       </c>
       <c r="AL58" s="8" t="n"/>
       <c r="AM58" s="8" t="n"/>
@@ -17431,10 +17579,10 @@
       <c r="AH59" s="9" t="n"/>
       <c r="AI59" s="9" t="n"/>
       <c r="AJ59" s="9" t="n"/>
-      <c r="AK59" s="9" t="n"/>
-      <c r="AL59" s="9" t="n">
+      <c r="AK59" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n"/>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -17534,7 +17682,7 @@
       <c r="AK61" s="9" t="n"/>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n">
-        <v>12</v>
+        <v>11.494</v>
       </c>
       <c r="AN61" s="9" t="n"/>
       <c r="AO61" s="9" t="n"/>
@@ -17629,9 +17777,7 @@
       <c r="AH63" s="9" t="n"/>
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
-      <c r="AK63" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="AK63" s="9" t="n"/>
       <c r="AL63" s="9" t="n"/>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
@@ -17683,11 +17829,13 @@
       <c r="AL64" s="8" t="n"/>
       <c r="AM64" s="8" t="n"/>
       <c r="AN64" s="8" t="n">
-        <v>0.6</v>
+        <v>0.533</v>
       </c>
       <c r="AO64" s="8" t="n"/>
       <c r="AP64" s="8" t="n"/>
-      <c r="AQ64" s="8" t="n"/>
+      <c r="AQ64" s="8" t="n">
+        <v>0.067</v>
+      </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="19">
       <c r="B65" s="10" t="inlineStr">
@@ -18182,11 +18330,13 @@
       <c r="AK74" s="8" t="n"/>
       <c r="AL74" s="8" t="n"/>
       <c r="AM74" s="8" t="n"/>
-      <c r="AN74" s="8" t="n"/>
+      <c r="AN74" s="8" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AO74" s="8" t="n"/>
       <c r="AP74" s="8" t="n"/>
       <c r="AQ74" s="8" t="n">
-        <v>0.6</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="75" ht="12" customHeight="1" s="19">
@@ -18334,10 +18484,12 @@
       <c r="AM77" s="9" t="n"/>
       <c r="AN77" s="9" t="n"/>
       <c r="AO77" s="9" t="n">
-        <v>0.6</v>
+        <v>0.593</v>
       </c>
       <c r="AP77" s="9" t="n"/>
-      <c r="AQ77" s="9" t="n"/>
+      <c r="AQ77" s="9" t="n">
+        <v>0.007</v>
+      </c>
     </row>
     <row r="78" ht="12" customHeight="1" s="19">
       <c r="B78" s="10" t="inlineStr">
@@ -18434,7 +18586,7 @@
       <c r="AM79" s="9" t="n"/>
       <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -18471,7 +18623,7 @@
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
       <c r="AB80" s="8" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
@@ -18524,11 +18676,11 @@
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n"/>
+      <c r="AF81" s="9" t="n">
+        <v>0.543</v>
+      </c>
       <c r="AG81" s="9" t="n"/>
-      <c r="AH81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
       <c r="AJ81" s="9" t="n"/>
       <c r="AK81" s="9" t="n"/>
@@ -18571,12 +18723,12 @@
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n"/>
+      <c r="AC82" s="8" t="n">
+        <v>0.595</v>
+      </c>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
-      <c r="AF82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
       <c r="AI82" s="8" t="n"/>
@@ -18621,10 +18773,10 @@
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
-      <c r="AC83" s="9" t="n">
+      <c r="AC83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD83" s="9" t="n"/>
       <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
@@ -19011,13 +19163,15 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
+      <c r="D2" s="8" t="n">
+        <v>41.42</v>
+      </c>
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n">
-        <v>80</v>
+        <v>38.58</v>
       </c>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
@@ -19064,7 +19218,7 @@
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="9" t="n">
-        <v>55</v>
+        <v>53.801</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
@@ -19121,7 +19275,7 @@
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n">
-        <v>35</v>
+        <v>30.295</v>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
@@ -19166,11 +19320,11 @@
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n">
         <v>72</v>
       </c>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
@@ -19219,10 +19373,10 @@
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="I6" s="8" t="n"/>
       <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
@@ -19267,20 +19421,22 @@
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n">
-        <v>43.7</v>
+        <v>8.371</v>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
+      <c r="J7" s="9" t="n">
+        <v>41.145</v>
+      </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n">
-        <v>11.3</v>
+        <v>5.483</v>
       </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
@@ -19320,14 +19476,16 @@
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n">
-        <v>60</v>
+        <v>31.455</v>
       </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="J8" s="8" t="n">
+        <v>28.545</v>
+      </c>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
@@ -19425,10 +19583,10 @@
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n">
+      <c r="H10" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
@@ -19481,12 +19639,12 @@
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n">
-        <v>25</v>
+        <v>25.577</v>
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n">
-        <v>3</v>
+        <v>2.423</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -19529,7 +19687,7 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>25</v>
+        <v>23.236</v>
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -19579,7 +19737,7 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n">
-        <v>86</v>
+        <v>82.755</v>
       </c>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
@@ -19631,11 +19789,11 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
@@ -19678,19 +19836,23 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="9" t="n">
+        <v>20.484</v>
+      </c>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n">
-        <v>37.421</v>
+        <v>18.514</v>
       </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
+      <c r="L15" s="9" t="n">
+        <v>0.298</v>
+      </c>
       <c r="M15" s="9" t="n">
-        <v>6.579</v>
+        <v>4.704</v>
       </c>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
@@ -19789,14 +19951,14 @@
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n">
-        <v>22.895</v>
+        <v>17.128</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n">
-        <v>2.105</v>
+        <v>5.892</v>
       </c>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
@@ -19843,16 +20005,16 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n">
-        <v>13.25</v>
+        <v>17.553</v>
       </c>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n">
-        <v>11.75</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n">
-        <v>35</v>
+        <v>33.587</v>
       </c>
       <c r="Q18" s="8" t="n"/>
       <c r="R18" s="8" t="n"/>
@@ -19890,7 +20052,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>45</v>
+        <v>43.74</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
@@ -19943,16 +20105,18 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="n">
+        <v>25.538</v>
+      </c>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
+      <c r="M20" s="8" t="n">
+        <v>9.462</v>
+      </c>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
@@ -19996,11 +20160,11 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
+      <c r="H21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -20094,9 +20258,11 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D23" s="9" t="n"/>
+        <v>6.251</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>6.749</v>
+      </c>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
@@ -20149,10 +20315,10 @@
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
@@ -20196,7 +20362,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>18</v>
+        <v>14.998</v>
       </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
@@ -20246,16 +20412,16 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
+      <c r="J26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
@@ -20298,7 +20464,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>20</v>
+        <v>19.483</v>
       </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
@@ -20368,10 +20534,10 @@
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
-      <c r="W28" s="8" t="n"/>
-      <c r="X28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="W28" s="8" t="n">
+        <v>14.917</v>
+      </c>
+      <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
       <c r="Z28" s="8" t="n"/>
       <c r="AA28" s="8" t="n"/>
@@ -20427,7 +20593,7 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n">
-        <v>10</v>
+        <v>9.329000000000001</v>
       </c>
       <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
@@ -20469,15 +20635,17 @@
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
-      <c r="V30" s="8" t="n"/>
-      <c r="W30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="V30" s="8" t="n">
+        <v>11.893</v>
+      </c>
+      <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n">
+        <v>2.107</v>
+      </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
@@ -20519,7 +20687,7 @@
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n">
-        <v>6</v>
+        <v>5.707</v>
       </c>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
@@ -20570,11 +20738,11 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n">
-        <v>7.44</v>
+        <v>7.579</v>
       </c>
       <c r="U32" s="8" t="n"/>
       <c r="V32" s="8" t="n">
-        <v>2.56</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
@@ -20621,17 +20789,23 @@
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
-      <c r="S33" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
-      <c r="U33" s="9" t="n"/>
-      <c r="V33" s="9" t="n"/>
+      <c r="U33" s="9" t="n">
+        <v>3.143</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>0.245</v>
+      </c>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="AA33" s="9" t="n">
+        <v>1.15</v>
+      </c>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n"/>
       <c r="AD33" s="9" t="n"/>
@@ -20672,30 +20846,32 @@
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="n"/>
-      <c r="S34" s="8" t="n"/>
+      <c r="S34" s="8" t="n">
+        <v>12.31</v>
+      </c>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n">
-        <v>0.3</v>
+        <v>2.606</v>
       </c>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n">
-        <v>0.439</v>
+        <v>2.489</v>
       </c>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
       <c r="AG34" s="8" t="n">
-        <v>0.75</v>
+        <v>4.107</v>
       </c>
       <c r="AH34" s="8" t="n"/>
       <c r="AI34" s="8" t="n">
-        <v>0.36</v>
+        <v>0.488</v>
       </c>
       <c r="AJ34" s="8" t="n"/>
       <c r="AK34" s="8" t="n"/>
@@ -20728,27 +20904,35 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="S35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n">
+        <v>8.827999999999999</v>
+      </c>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n">
+        <v>0.198</v>
+      </c>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n">
+        <v>1.519</v>
+      </c>
       <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="AD35" s="9" t="n">
+        <v>1.539</v>
+      </c>
       <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
       <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="9" t="n"/>
+      <c r="AJ35" s="9" t="n">
+        <v>7.916</v>
+      </c>
       <c r="AK35" s="9" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="9" t="n"/>
@@ -20780,9 +20964,7 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
-      <c r="S36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S36" s="8" t="n"/>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
@@ -20794,7 +20976,9 @@
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
-      <c r="AE36" s="8" t="n"/>
+      <c r="AE36" s="8" t="n">
+        <v>0.587</v>
+      </c>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
       <c r="AH36" s="8" t="n"/>
@@ -20831,24 +21015,30 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
+      <c r="S37" s="9" t="n">
+        <v>0.234</v>
+      </c>
       <c r="T37" s="9" t="n"/>
-      <c r="U37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.107</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="9" t="n"/>
+      <c r="AE37" s="9" t="n">
+        <v>0.08599999999999999</v>
+      </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.174</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -20882,11 +21072,11 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
-      <c r="S38" s="8" t="n"/>
+      <c r="S38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T38" s="8" t="n"/>
-      <c r="U38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
       <c r="X38" s="8" t="n"/>
@@ -20933,11 +21123,11 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n"/>
+      <c r="S39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T39" s="9" t="n"/>
-      <c r="U39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
@@ -20984,11 +21174,11 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
-      <c r="S40" s="8" t="n"/>
+      <c r="S40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T40" s="8" t="n"/>
-      <c r="U40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
@@ -21035,11 +21225,11 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n"/>
+      <c r="S41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T41" s="9" t="n"/>
-      <c r="U41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n"/>
@@ -21188,14 +21378,14 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -21241,12 +21431,12 @@
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
-      <c r="U45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
-      <c r="X45" s="9" t="n"/>
+      <c r="X45" s="9" t="n">
+        <v>0.587</v>
+      </c>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -21292,12 +21482,12 @@
       <c r="R46" s="8" t="n"/>
       <c r="S46" s="8" t="n"/>
       <c r="T46" s="8" t="n"/>
-      <c r="U46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -21346,16 +21536,16 @@
       <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
-      <c r="X47" s="9" t="n"/>
+      <c r="X47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y47" s="9" t="n"/>
       <c r="Z47" s="9" t="n"/>
       <c r="AA47" s="9" t="n"/>
       <c r="AB47" s="9" t="n"/>
       <c r="AC47" s="9" t="n"/>
       <c r="AD47" s="9" t="n"/>
-      <c r="AE47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE47" s="9" t="n"/>
       <c r="AF47" s="9" t="n"/>
       <c r="AG47" s="9" t="n"/>
       <c r="AH47" s="9" t="n"/>
@@ -21397,16 +21587,16 @@
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
-      <c r="X48" s="8" t="n"/>
+      <c r="X48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y48" s="8" t="n"/>
       <c r="Z48" s="8" t="n"/>
       <c r="AA48" s="8" t="n"/>
       <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="n"/>
-      <c r="AE48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE48" s="8" t="n"/>
       <c r="AF48" s="8" t="n"/>
       <c r="AG48" s="8" t="n"/>
       <c r="AH48" s="8" t="n"/>
@@ -21444,7 +21634,7 @@
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
@@ -21495,7 +21685,7 @@
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n">
-        <v>0.6</v>
+        <v>0.528</v>
       </c>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
@@ -21546,7 +21736,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.487</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -21554,7 +21744,9 @@
       <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
       <c r="Y51" s="9" t="n"/>
-      <c r="Z51" s="9" t="n"/>
+      <c r="Z51" s="9" t="n">
+        <v>0.113</v>
+      </c>
       <c r="AA51" s="9" t="n"/>
       <c r="AB51" s="9" t="n"/>
       <c r="AC51" s="9" t="n"/>
@@ -21596,14 +21788,14 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S52" s="8" t="n"/>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n"/>
+      <c r="X52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
@@ -21648,7 +21840,7 @@
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="9" t="n">
-        <v>0.6</v>
+        <v>0.569</v>
       </c>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
@@ -21698,14 +21890,14 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
+      <c r="S54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
       <c r="W54" s="8" t="n"/>
-      <c r="X54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X54" s="8" t="n"/>
       <c r="Y54" s="8" t="n"/>
       <c r="Z54" s="8" t="n"/>
       <c r="AA54" s="8" t="n"/>
@@ -21749,14 +21941,14 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
+      <c r="S55" s="9" t="n">
+        <v>0.466</v>
+      </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
       <c r="W55" s="9" t="n"/>
-      <c r="X55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X55" s="9" t="n"/>
       <c r="Y55" s="9" t="n"/>
       <c r="Z55" s="9" t="n"/>
       <c r="AA55" s="9" t="n"/>
@@ -21766,7 +21958,9 @@
       <c r="AE55" s="9" t="n"/>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
-      <c r="AH55" s="9" t="n"/>
+      <c r="AH55" s="9" t="n">
+        <v>0.134</v>
+      </c>
       <c r="AI55" s="9" t="n"/>
       <c r="AJ55" s="9" t="n"/>
       <c r="AK55" s="9" t="n"/>
@@ -21826,7 +22020,7 @@
       <c r="AI56" s="8" t="n"/>
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n">
-        <v>15</v>
+        <v>14.58</v>
       </c>
       <c r="AL56" s="8" t="n"/>
       <c r="AM56" s="8" t="n"/>
@@ -21877,7 +22071,7 @@
       <c r="AJ57" s="9" t="n"/>
       <c r="AK57" s="9" t="n"/>
       <c r="AL57" s="9" t="n">
-        <v>10</v>
+        <v>9.846</v>
       </c>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
@@ -21927,7 +22121,7 @@
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n"/>
       <c r="AL58" s="8" t="n">
-        <v>14</v>
+        <v>13.35</v>
       </c>
       <c r="AM58" s="8" t="n"/>
       <c r="AN58" s="8" t="n"/>
@@ -21978,7 +22172,7 @@
       <c r="AK59" s="9" t="n"/>
       <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n">
-        <v>6</v>
+        <v>5.875</v>
       </c>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -22026,7 +22220,7 @@
       <c r="AI60" s="8" t="n"/>
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n">
-        <v>10</v>
+        <v>9.611000000000001</v>
       </c>
       <c r="AL60" s="8" t="n"/>
       <c r="AM60" s="8" t="n"/>
@@ -22128,7 +22322,7 @@
       <c r="AK62" s="8" t="n"/>
       <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n">
-        <v>6</v>
+        <v>7.994</v>
       </c>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
@@ -22176,7 +22370,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>6.634</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -22277,7 +22473,7 @@
       <c r="AL65" s="9" t="n"/>
       <c r="AM65" s="9" t="n"/>
       <c r="AN65" s="9" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="AO65" s="9" t="n"/>
       <c r="AP65" s="9" t="n"/>
@@ -23014,12 +23210,12 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
-      <c r="AB80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB80" s="8" t="n"/>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
-      <c r="AE80" s="8" t="n"/>
+      <c r="AE80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
       <c r="AH80" s="8" t="n"/>
@@ -23068,11 +23264,11 @@
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n"/>
+      <c r="AF81" s="9" t="n">
+        <v>0.496</v>
+      </c>
       <c r="AG81" s="9" t="n"/>
-      <c r="AH81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
       <c r="AJ81" s="9" t="n"/>
       <c r="AK81" s="9" t="n"/>
@@ -23110,7 +23306,9 @@
       <c r="U82" s="8" t="n"/>
       <c r="V82" s="8" t="n"/>
       <c r="W82" s="8" t="n"/>
-      <c r="X82" s="8" t="n"/>
+      <c r="X82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y82" s="8" t="n"/>
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
@@ -23118,9 +23316,7 @@
       <c r="AC82" s="8" t="n"/>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
-      <c r="AF82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
       <c r="AI82" s="8" t="n"/>
@@ -23165,10 +23361,10 @@
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
-      <c r="AC83" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AD83" s="9" t="n"/>
+      <c r="AC83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n">
+        <v>0.5590000000000001</v>
+      </c>
       <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
@@ -23555,13 +23751,13 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
@@ -23614,13 +23810,13 @@
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n">
-        <v>47.619</v>
+        <v>49.815</v>
       </c>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n">
-        <v>7.381</v>
+        <v>4.063</v>
       </c>
       <c r="P3" s="9" t="n"/>
       <c r="Q3" s="9" t="n"/>
@@ -23660,7 +23856,7 @@
       </c>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n">
-        <v>35</v>
+        <v>34.61</v>
       </c>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
@@ -23710,13 +23906,15 @@
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
+      <c r="D5" s="9" t="n">
+        <v>38.743</v>
+      </c>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n">
-        <v>72</v>
+        <v>33.257</v>
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
@@ -23763,7 +23961,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n">
-        <v>56</v>
+        <v>48.969</v>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -23773,7 +23971,7 @@
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n">
-        <v>12</v>
+        <v>15.684</v>
       </c>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -23916,11 +24114,11 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n"/>
@@ -23967,15 +24165,17 @@
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="J10" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -24019,12 +24219,14 @@
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
+      <c r="H11" s="9" t="n">
+        <v>14</v>
+      </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
@@ -24078,7 +24280,7 @@
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n">
-        <v>25</v>
+        <v>24.62</v>
       </c>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
@@ -24124,11 +24326,11 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
+      <c r="H13" s="9" t="n">
+        <v>86</v>
+      </c>
       <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n">
-        <v>86</v>
-      </c>
+      <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
@@ -24174,11 +24376,13 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>55</v>
+        <v>33.642</v>
       </c>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
+      <c r="I14" s="8" t="n">
+        <v>21.358</v>
+      </c>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
@@ -24222,15 +24426,15 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="J15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
@@ -24276,7 +24480,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>45.121</v>
+        <v>40.888</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -24287,7 +24491,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>4.879</v>
+        <v>6.317</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -24330,7 +24534,7 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
-        <v>25</v>
+        <v>24.504</v>
       </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -24377,7 +24581,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>60</v>
+        <v>57.873</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
@@ -24480,24 +24684,24 @@
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n">
-        <v>9.157999999999999</v>
+        <v>3.93</v>
       </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n">
-        <v>3.416</v>
+        <v>2.654</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>17.895</v>
+        <v>22.872</v>
       </c>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n">
-        <v>4.532</v>
+        <v>5.544</v>
       </c>
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="n"/>
@@ -24540,11 +24744,11 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -24592,16 +24796,24 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I22" s="8" t="n"/>
+        <v>4.305</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>4.171</v>
+      </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
+      <c r="M22" s="8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>5.172</v>
+      </c>
       <c r="O22" s="8" t="n"/>
-      <c r="P22" s="8" t="n"/>
+      <c r="P22" s="8" t="n">
+        <v>0.522</v>
+      </c>
       <c r="Q22" s="8" t="n"/>
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
@@ -24643,14 +24855,14 @@
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
+      <c r="I23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
@@ -24688,16 +24900,18 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
+      <c r="C24" s="8" t="n">
+        <v>10.268</v>
+      </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
+      <c r="E24" s="8" t="n">
+        <v>4.732</v>
+      </c>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
@@ -24744,11 +24958,11 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
@@ -24792,12 +25006,12 @@
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
+      <c r="E26" s="8" t="n">
+        <v>0.506</v>
+      </c>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
@@ -24909,7 +25123,7 @@
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n">
-        <v>4.587</v>
+        <v>3.64</v>
       </c>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
@@ -24922,7 +25136,7 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n">
-        <v>10.413</v>
+        <v>11.36</v>
       </c>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
@@ -24961,13 +25175,13 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
-      <c r="W29" s="9" t="n"/>
+      <c r="W29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
@@ -25014,20 +25228,18 @@
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n">
-        <v>13.44</v>
+        <v>11.541</v>
       </c>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n">
-        <v>0.3</v>
+        <v>2.459</v>
       </c>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n">
-        <v>0.26</v>
-      </c>
+      <c r="AB30" s="8" t="n"/>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
@@ -25067,12 +25279,14 @@
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="n"/>
+      <c r="S31" s="9" t="n">
+        <v>0.93</v>
+      </c>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
       <c r="W31" s="9" t="n">
-        <v>6</v>
+        <v>5.07</v>
       </c>
       <c r="X31" s="9" t="n"/>
       <c r="Y31" s="9" t="n"/>
@@ -25120,24 +25334,32 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
-      <c r="U32" s="8" t="n"/>
+      <c r="U32" s="8" t="n">
+        <v>4.912</v>
+      </c>
       <c r="V32" s="8" t="n"/>
-      <c r="W32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="n"/>
-      <c r="AA32" s="8" t="n"/>
+      <c r="Z32" s="8" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AA32" s="8" t="n">
+        <v>2.028</v>
+      </c>
       <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="8" t="n"/>
+      <c r="AC32" s="8" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AD32" s="8" t="n"/>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
       <c r="AG32" s="8" t="n"/>
       <c r="AH32" s="8" t="n"/>
       <c r="AI32" s="8" t="n"/>
-      <c r="AJ32" s="8" t="n"/>
+      <c r="AJ32" s="8" t="n">
+        <v>1.101</v>
+      </c>
       <c r="AK32" s="8" t="n"/>
       <c r="AL32" s="8" t="n"/>
       <c r="AM32" s="8" t="n"/>
@@ -25176,7 +25398,7 @@
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n">
-        <v>0.333</v>
+        <v>0.997</v>
       </c>
       <c r="Z33" s="9" t="n"/>
       <c r="AA33" s="9" t="n"/>
@@ -25186,15 +25408,13 @@
       <c r="AE33" s="9" t="n"/>
       <c r="AF33" s="9" t="n"/>
       <c r="AG33" s="9" t="n">
-        <v>0.75</v>
+        <v>1.399</v>
       </c>
       <c r="AH33" s="9" t="n"/>
       <c r="AI33" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AJ33" s="9" t="n">
-        <v>0.327</v>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="AJ33" s="9" t="n"/>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="9" t="n"/>
@@ -25227,12 +25447,12 @@
       <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n">
-        <v>15</v>
+        <v>17.044</v>
       </c>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
@@ -25240,13 +25460,13 @@
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n">
-        <v>0.17</v>
+        <v>1.138</v>
       </c>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n">
-        <v>0.037</v>
+        <v>1.274</v>
       </c>
       <c r="AG34" s="8" t="n"/>
       <c r="AH34" s="8" t="n"/>
@@ -25282,10 +25502,10 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n">
+      <c r="R35" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
@@ -25334,7 +25554,9 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
-      <c r="S36" s="8" t="n"/>
+      <c r="S36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
@@ -25346,9 +25568,7 @@
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
-      <c r="AE36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE36" s="8" t="n"/>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
       <c r="AH36" s="8" t="n"/>
@@ -25390,9 +25610,7 @@
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="X37" s="9" t="n"/>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
@@ -25400,13 +25618,11 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="AH37" s="9" t="n"/>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -25644,14 +25860,14 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
-      <c r="S42" s="8" t="n"/>
+      <c r="S42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X42" s="8" t="n"/>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -25695,13 +25911,15 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n"/>
+      <c r="S43" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
       <c r="X43" s="9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
@@ -25746,14 +25964,14 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n"/>
+      <c r="S44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X44" s="8" t="n"/>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -25797,14 +26015,14 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n"/>
+      <c r="S45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
-      <c r="X45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X45" s="9" t="n"/>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -25848,14 +26066,14 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
-      <c r="S46" s="8" t="n"/>
+      <c r="S46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X46" s="8" t="n"/>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -25950,7 +26168,9 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
-      <c r="S48" s="8" t="n"/>
+      <c r="S48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
@@ -25962,9 +26182,7 @@
       <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="n"/>
-      <c r="AE48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE48" s="8" t="n"/>
       <c r="AF48" s="8" t="n"/>
       <c r="AG48" s="8" t="n"/>
       <c r="AH48" s="8" t="n"/>
@@ -26002,7 +26220,7 @@
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
@@ -26053,7 +26271,7 @@
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n">
-        <v>0.6</v>
+        <v>0.585</v>
       </c>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
@@ -26104,7 +26322,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.534</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -26117,7 +26335,9 @@
       <c r="AB51" s="9" t="n"/>
       <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9" t="n"/>
-      <c r="AE51" s="9" t="n"/>
+      <c r="AE51" s="9" t="n">
+        <v>0.066</v>
+      </c>
       <c r="AF51" s="9" t="n"/>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n"/>
@@ -26154,9 +26374,7 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S52" s="8" t="n"/>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
@@ -26171,7 +26389,9 @@
       <c r="AE52" s="8" t="n"/>
       <c r="AF52" s="8" t="n"/>
       <c r="AG52" s="8" t="n"/>
-      <c r="AH52" s="8" t="n"/>
+      <c r="AH52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AI52" s="8" t="n"/>
       <c r="AJ52" s="8" t="n"/>
       <c r="AK52" s="8" t="n"/>
@@ -26257,7 +26477,7 @@
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
       <c r="S54" s="8" t="n">
-        <v>0.6</v>
+        <v>0.597</v>
       </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
@@ -26307,14 +26527,14 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
+      <c r="S55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
       <c r="W55" s="9" t="n"/>
-      <c r="X55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X55" s="9" t="n"/>
       <c r="Y55" s="9" t="n"/>
       <c r="Z55" s="9" t="n"/>
       <c r="AA55" s="9" t="n"/>
@@ -26433,10 +26653,10 @@
       <c r="AH57" s="9" t="n"/>
       <c r="AI57" s="9" t="n"/>
       <c r="AJ57" s="9" t="n"/>
-      <c r="AK57" s="9" t="n"/>
-      <c r="AL57" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="AK57" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL57" s="9" t="n"/>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
       <c r="AO57" s="9" t="n"/>
@@ -26484,7 +26704,7 @@
       <c r="AI58" s="8" t="n"/>
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n">
-        <v>14</v>
+        <v>11.595</v>
       </c>
       <c r="AL58" s="8" t="n"/>
       <c r="AM58" s="8" t="n"/>
@@ -26533,10 +26753,10 @@
       <c r="AH59" s="9" t="n"/>
       <c r="AI59" s="9" t="n"/>
       <c r="AJ59" s="9" t="n"/>
-      <c r="AK59" s="9" t="n"/>
-      <c r="AL59" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="AK59" s="9" t="n">
+        <v>5.512</v>
+      </c>
+      <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n"/>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -26585,7 +26805,7 @@
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n"/>
       <c r="AL60" s="8" t="n">
-        <v>10</v>
+        <v>9.952</v>
       </c>
       <c r="AM60" s="8" t="n"/>
       <c r="AN60" s="8" t="n"/>
@@ -26636,7 +26856,7 @@
       <c r="AK61" s="9" t="n"/>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n">
-        <v>12</v>
+        <v>10.948</v>
       </c>
       <c r="AN61" s="9" t="n"/>
       <c r="AO61" s="9" t="n"/>
@@ -26683,7 +26903,9 @@
       <c r="AH62" s="8" t="n"/>
       <c r="AI62" s="8" t="n"/>
       <c r="AJ62" s="8" t="n"/>
-      <c r="AK62" s="8" t="n"/>
+      <c r="AK62" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
       <c r="AN62" s="8" t="n"/>
@@ -26731,9 +26953,7 @@
       <c r="AH63" s="9" t="n"/>
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
-      <c r="AK63" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="AK63" s="9" t="n"/>
       <c r="AL63" s="9" t="n"/>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
@@ -27135,10 +27355,12 @@
       <c r="AL71" s="9" t="n"/>
       <c r="AM71" s="9" t="n"/>
       <c r="AN71" s="9" t="n"/>
-      <c r="AO71" s="9" t="n"/>
+      <c r="AO71" s="9" t="n">
+        <v>0.185</v>
+      </c>
       <c r="AP71" s="9" t="n"/>
       <c r="AQ71" s="9" t="n">
-        <v>0.6</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="19">
@@ -27434,9 +27656,11 @@
       <c r="AK77" s="9" t="n"/>
       <c r="AL77" s="9" t="n"/>
       <c r="AM77" s="9" t="n"/>
-      <c r="AN77" s="9" t="n"/>
+      <c r="AN77" s="9" t="n">
+        <v>0.187</v>
+      </c>
       <c r="AO77" s="9" t="n">
-        <v>0.6</v>
+        <v>0.328</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -27536,7 +27760,7 @@
       <c r="AM79" s="9" t="n"/>
       <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -27572,12 +27796,12 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
-      <c r="AB80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB80" s="8" t="n"/>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
-      <c r="AE80" s="8" t="n"/>
+      <c r="AE80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
       <c r="AH80" s="8" t="n"/>
@@ -27618,7 +27842,9 @@
       <c r="U81" s="9" t="n"/>
       <c r="V81" s="9" t="n"/>
       <c r="W81" s="9" t="n"/>
-      <c r="X81" s="9" t="n"/>
+      <c r="X81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y81" s="9" t="n"/>
       <c r="Z81" s="9" t="n"/>
       <c r="AA81" s="9" t="n"/>
@@ -27626,9 +27852,7 @@
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AF81" s="9" t="n"/>
       <c r="AG81" s="9" t="n"/>
       <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
@@ -27674,7 +27898,7 @@
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
       <c r="AC82" s="8" t="n">
-        <v>0.6</v>
+        <v>0.268</v>
       </c>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
@@ -27715,12 +27939,12 @@
       <c r="R83" s="9" t="n"/>
       <c r="S83" s="9" t="n"/>
       <c r="T83" s="9" t="n"/>
-      <c r="U83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
-      <c r="X83" s="9" t="n"/>
+      <c r="X83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y83" s="9" t="n"/>
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
@@ -28223,7 +28447,7 @@
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n">
-        <v>35</v>
+        <v>34.618</v>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
@@ -28369,7 +28593,7 @@
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n">
-        <v>43.7</v>
+        <v>43.511</v>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -28382,7 +28606,7 @@
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n">
-        <v>11.3</v>
+        <v>11.489</v>
       </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
@@ -28525,11 +28749,11 @@
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
@@ -28583,12 +28807,12 @@
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n">
-        <v>25</v>
+        <v>23.125</v>
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n">
-        <v>3</v>
+        <v>1.494</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -28631,7 +28855,7 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>25</v>
+        <v>24.884</v>
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -28680,11 +28904,11 @@
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
+      <c r="F13" s="9" t="n">
+        <v>86</v>
+      </c>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n">
-        <v>86</v>
-      </c>
+      <c r="H13" s="9" t="n"/>
       <c r="I13" s="9" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n"/>
@@ -28835,11 +29059,11 @@
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
+      <c r="H16" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n">
-        <v>50</v>
-      </c>
+      <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
@@ -28889,15 +29113,13 @@
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n">
-        <v>22.895</v>
+        <v>25</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n">
-        <v>2.105</v>
-      </c>
+      <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
@@ -28943,16 +29165,16 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n">
-        <v>13.25</v>
+        <v>13.629</v>
       </c>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n">
-        <v>11.75</v>
+        <v>10.791</v>
       </c>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n">
-        <v>35</v>
+        <v>35.58</v>
       </c>
       <c r="Q18" s="8" t="n"/>
       <c r="R18" s="8" t="n"/>
@@ -29092,17 +29314,17 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>3.646</v>
+        <v>0.61</v>
       </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n">
-        <v>6.828</v>
+        <v>7.262</v>
       </c>
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n">
-        <v>9.526</v>
+        <v>12.129</v>
       </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
@@ -29146,16 +29368,16 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n"/>
+      <c r="C22" s="8" t="n">
+        <v>13.903</v>
+      </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
@@ -29250,23 +29472,19 @@
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n">
-        <v>1.111</v>
-      </c>
+      <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="J24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>0.209</v>
-      </c>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
       <c r="R24" s="8" t="n"/>
@@ -29303,16 +29521,16 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
+        <v>17.062</v>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
@@ -29405,16 +29623,16 @@
           <t>C6</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
+      <c r="J27" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
@@ -29477,7 +29695,7 @@
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n">
-        <v>15</v>
+        <v>14.988</v>
       </c>
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
@@ -29523,7 +29741,9 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n"/>
+      <c r="S29" s="9" t="n">
+        <v>5.2</v>
+      </c>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
@@ -29535,7 +29755,7 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
@@ -29575,12 +29795,12 @@
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n">
-        <v>5.68</v>
+        <v>1.615</v>
       </c>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n">
-        <v>8.32</v>
+        <v>11.87</v>
       </c>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
@@ -29595,7 +29815,9 @@
       <c r="AG30" s="8" t="n"/>
       <c r="AH30" s="8" t="n"/>
       <c r="AI30" s="8" t="n"/>
-      <c r="AJ30" s="8" t="n"/>
+      <c r="AJ30" s="8" t="n">
+        <v>0.515</v>
+      </c>
       <c r="AK30" s="8" t="n"/>
       <c r="AL30" s="8" t="n"/>
       <c r="AM30" s="8" t="n"/>
@@ -29629,7 +29851,7 @@
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n">
-        <v>6</v>
+        <v>5.925</v>
       </c>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
@@ -29680,11 +29902,11 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n">
-        <v>7.44</v>
+        <v>7.779</v>
       </c>
       <c r="U32" s="8" t="n"/>
       <c r="V32" s="8" t="n">
-        <v>2.56</v>
+        <v>2.221</v>
       </c>
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
@@ -29734,10 +29956,10 @@
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n">
-        <v>2.16</v>
+        <v>4.076</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>4.12</v>
+        <v>2.936</v>
       </c>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
@@ -29746,7 +29968,7 @@
         <v>1.087</v>
       </c>
       <c r="AA33" s="9" t="n">
-        <v>1.091</v>
+        <v>1.001</v>
       </c>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n"/>
@@ -29794,24 +30016,24 @@
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n">
-        <v>0.3</v>
+        <v>2.869</v>
       </c>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n">
-        <v>0.439</v>
+        <v>1.065</v>
       </c>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
       <c r="AG34" s="8" t="n">
-        <v>0.75</v>
+        <v>1.043</v>
       </c>
       <c r="AH34" s="8" t="n"/>
       <c r="AI34" s="8" t="n">
-        <v>0.36</v>
+        <v>2.215</v>
       </c>
       <c r="AJ34" s="8" t="n"/>
       <c r="AK34" s="8" t="n"/>
@@ -29844,21 +30066,25 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n">
+        <v>0.234</v>
+      </c>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n">
+        <v>0.463</v>
+      </c>
       <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="AD35" s="9" t="n">
+        <v>5.936</v>
+      </c>
       <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
@@ -29896,7 +30122,9 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
-      <c r="S36" s="8" t="n"/>
+      <c r="S36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
@@ -29908,9 +30136,7 @@
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
-      <c r="AE36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE36" s="8" t="n"/>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
       <c r="AH36" s="8" t="n"/>
@@ -29953,7 +30179,7 @@
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="9" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
@@ -29962,12 +30188,12 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.27</v>
+        <v>0.283</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n">
-        <v>0.3</v>
+        <v>0.228</v>
       </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
@@ -30002,14 +30228,14 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
-      <c r="S38" s="8" t="n"/>
+      <c r="S38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X38" s="8" t="n"/>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
@@ -30053,14 +30279,14 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n"/>
+      <c r="S39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
-      <c r="X39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X39" s="9" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
       <c r="AA39" s="9" t="n"/>
@@ -30161,7 +30387,7 @@
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
@@ -30314,7 +30540,7 @@
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
       <c r="X44" s="8" t="n">
-        <v>0.6</v>
+        <v>0.579</v>
       </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
@@ -30365,7 +30591,7 @@
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
       <c r="X45" s="9" t="n">
-        <v>0.6</v>
+        <v>0.555</v>
       </c>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
@@ -30513,7 +30739,7 @@
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n">
-        <v>0.6</v>
+        <v>0.537</v>
       </c>
       <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
@@ -30666,7 +30892,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.597</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -30717,7 +30943,7 @@
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
       <c r="S52" s="8" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
@@ -30768,7 +30994,7 @@
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="9" t="n">
-        <v>0.6</v>
+        <v>0.472</v>
       </c>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
@@ -30784,7 +31010,9 @@
       <c r="AE53" s="9" t="n"/>
       <c r="AF53" s="9" t="n"/>
       <c r="AG53" s="9" t="n"/>
-      <c r="AH53" s="9" t="n"/>
+      <c r="AH53" s="9" t="n">
+        <v>0.036</v>
+      </c>
       <c r="AI53" s="9" t="n"/>
       <c r="AJ53" s="9" t="n"/>
       <c r="AK53" s="9" t="n"/>
@@ -30869,9 +31097,7 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S55" s="9" t="n"/>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
@@ -30882,7 +31108,9 @@
       <c r="AA55" s="9" t="n"/>
       <c r="AB55" s="9" t="n"/>
       <c r="AC55" s="9" t="n"/>
-      <c r="AD55" s="9" t="n"/>
+      <c r="AD55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AE55" s="9" t="n"/>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
@@ -30946,7 +31174,7 @@
       <c r="AI56" s="8" t="n"/>
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n">
-        <v>15</v>
+        <v>14.234</v>
       </c>
       <c r="AL56" s="8" t="n"/>
       <c r="AM56" s="8" t="n"/>
@@ -30997,7 +31225,7 @@
       <c r="AJ57" s="9" t="n"/>
       <c r="AK57" s="9" t="n"/>
       <c r="AL57" s="9" t="n">
-        <v>10</v>
+        <v>9.672000000000001</v>
       </c>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
@@ -31098,7 +31326,7 @@
       <c r="AK59" s="9" t="n"/>
       <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n">
-        <v>6</v>
+        <v>5.777</v>
       </c>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -31146,7 +31374,7 @@
       <c r="AI60" s="8" t="n"/>
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n">
-        <v>10</v>
+        <v>9.788</v>
       </c>
       <c r="AL60" s="8" t="n"/>
       <c r="AM60" s="8" t="n"/>
@@ -31196,7 +31424,7 @@
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="9" t="n"/>
       <c r="AK61" s="9" t="n">
-        <v>5</v>
+        <v>6.896</v>
       </c>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n"/>
@@ -31248,7 +31476,7 @@
       <c r="AK62" s="8" t="n"/>
       <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n">
-        <v>6</v>
+        <v>7.286</v>
       </c>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
@@ -31296,7 +31524,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>3.209</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -31800,7 +32030,7 @@
       <c r="AO73" s="9" t="n"/>
       <c r="AP73" s="9" t="n"/>
       <c r="AQ73" s="9" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="19">
@@ -31946,11 +32176,13 @@
       <c r="AK76" s="8" t="n"/>
       <c r="AL76" s="8" t="n"/>
       <c r="AM76" s="8" t="n"/>
-      <c r="AN76" s="8" t="n"/>
+      <c r="AN76" s="8" t="n">
+        <v>0.027</v>
+      </c>
       <c r="AO76" s="8" t="n"/>
       <c r="AP76" s="8" t="n"/>
       <c r="AQ76" s="8" t="n">
-        <v>0.6</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="77" ht="12" customHeight="1" s="19">
@@ -31998,7 +32230,7 @@
       <c r="AM77" s="9" t="n"/>
       <c r="AN77" s="9" t="n"/>
       <c r="AO77" s="9" t="n">
-        <v>0.6</v>
+        <v>0.582</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -32048,7 +32280,7 @@
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n"/>
       <c r="AO78" s="8" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -32098,7 +32330,7 @@
       <c r="AM79" s="9" t="n"/>
       <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -32126,7 +32358,9 @@
       <c r="Q80" s="8" t="n"/>
       <c r="R80" s="8" t="n"/>
       <c r="S80" s="8" t="n"/>
-      <c r="T80" s="8" t="n"/>
+      <c r="T80" s="8" t="n">
+        <v>0.21</v>
+      </c>
       <c r="U80" s="8" t="n"/>
       <c r="V80" s="8" t="n"/>
       <c r="W80" s="8" t="n"/>
@@ -32135,7 +32369,7 @@
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
       <c r="AB80" s="8" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
@@ -32189,7 +32423,7 @@
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
       <c r="AF81" s="9" t="n">
-        <v>0.6</v>
+        <v>0.531</v>
       </c>
       <c r="AG81" s="9" t="n"/>
       <c r="AH81" s="9" t="n"/>
@@ -32235,11 +32469,11 @@
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n">
+      <c r="AC82" s="8" t="n"/>
+      <c r="AD82" s="8" t="n"/>
+      <c r="AE82" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD82" s="8" t="n"/>
-      <c r="AE82" s="8" t="n"/>
       <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
@@ -32286,10 +32520,10 @@
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
       <c r="AC83" s="9" t="n"/>
-      <c r="AD83" s="9" t="n">
+      <c r="AD83" s="9" t="n"/>
+      <c r="AE83" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
       <c r="AH83" s="9" t="n"/>
